--- a/data/trans_orig/P04C04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>284911</t>
+          <t>284947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344439</t>
+          <t>345265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251288</t>
+          <t>249108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283984</t>
+          <t>284152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>545279</t>
+          <t>549126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>616377</t>
+          <t>617597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29314</t>
+          <t>27467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>53637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111087</t>
+          <t>111019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>53797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>84258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>156523</t>
+          <t>152828</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353545</t>
+          <t>354647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387845</t>
+          <t>387232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235561</t>
+          <t>234548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451581</t>
+          <t>452284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579286</t>
+          <t>569076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827616</t>
+          <t>825757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60787</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272391</t>
+          <t>273359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92827</t>
+          <t>94752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346937</t>
+          <t>355045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>443509</t>
+          <t>443247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>477598</t>
+          <t>476936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>342659</t>
+          <t>307108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>510427</t>
+          <t>510429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>755162</t>
+          <t>790827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>974758</t>
+          <t>975411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>50135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81078</t>
+          <t>80768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71487</t>
+          <t>72281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241059</t>
+          <t>276075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134200</t>
+          <t>133079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358909</t>
+          <t>322250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>234960</t>
+          <t>258545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>742262</t>
+          <t>739905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>589829</t>
+          <t>588768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>623421</t>
+          <t>624518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>666102</t>
+          <t>694669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1351762</t>
+          <t>1354831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127261</t>
+          <t>128889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645311</t>
+          <t>620062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79836</t>
+          <t>78877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111795</t>
+          <t>112725</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221571</t>
+          <t>216532</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>922545</t>
+          <t>888093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>470830</t>
+          <t>470126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>499431</t>
+          <t>500438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>447057</t>
+          <t>446793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>471345</t>
+          <t>471723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>923686</t>
+          <t>924859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>962758</t>
+          <t>964863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>55589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>84831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72938</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96844</t>
+          <t>96312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135536</t>
+          <t>133791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174351</t>
+          <t>172767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>301167</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>322790</t>
+          <t>322177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>507341</t>
+          <t>510327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>581217</t>
+          <t>584242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>819809</t>
+          <t>820905</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>918738</t>
+          <t>916213</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64062</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93962</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>56291</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145098</t>
+          <t>146059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>227850</t>
+          <t>227508</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>247186</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>345465</t>
+          <t>346913</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365630</t>
+          <t>367272</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>578858</t>
+          <t>580232</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>608773</t>
+          <t>608683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,47 +3594,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7067</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3212</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>6759</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>51203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>54317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75207</t>
+          <t>74258</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91150</t>
+          <t>91931</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>120712</t>
+          <t>119649</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2102193</t>
+          <t>2147876</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2942420</t>
+          <t>2941233</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2889787</t>
+          <t>2872427</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3208364</t>
+          <t>3200684</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5102985</t>
+          <t>5088981</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6071938</t>
+          <t>6071245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>60444</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,47 +4085,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>79903</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>61555</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>101236</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>79903</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>60537</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>100332</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>463856</t>
+          <t>466962</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1317017</t>
+          <t>1275292</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>461788</t>
+          <t>461635</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>784780</t>
+          <t>791573</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>998771</t>
+          <t>1000538</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1989538</t>
+          <t>2000420</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>317374</t>
+          <t>324206</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>284947</t>
+          <t>293339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345265</t>
+          <t>349682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>313392</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249108</t>
+          <t>290678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284152</t>
+          <t>328182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>587759</t>
+          <t>637598</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>549126</t>
+          <t>600548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>617597</t>
+          <t>666831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78576</t>
+          <t>78435</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111019</t>
+          <t>110496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34886</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53797</t>
+          <t>61312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>119742</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84258</t>
+          <t>92160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152828</t>
+          <t>157040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>372579</t>
+          <t>419444</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354647</t>
+          <t>398544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387232</t>
+          <t>437055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>386487</t>
+          <t>435498</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234548</t>
+          <t>416324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452284</t>
+          <t>449141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>759067</t>
+          <t>854943</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569076</t>
+          <t>827795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825757</t>
+          <t>876274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -1294,67 +1294,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8801</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8331</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59303</t>
+          <t>63385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>120030</t>
+          <t>59861</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>273359</t>
+          <t>77407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>162496</t>
+          <t>106058</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94752</t>
+          <t>86201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355045</t>
+          <t>132133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>509310</t>
+          <t>498988</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509310</t>
+          <t>498988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>509310</t>
+          <t>498988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>932857</t>
+          <t>975878</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>932857</t>
+          <t>975878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932857</t>
+          <t>975878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>461599</t>
+          <t>537268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>443247</t>
+          <t>518398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>476936</t>
+          <t>554362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>464176</t>
+          <t>529958</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>514049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>510429</t>
+          <t>542747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>925776</t>
+          <t>1067226</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>790827</t>
+          <t>1044511</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>975411</t>
+          <t>1087218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64897</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50135</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80768</t>
+          <t>91272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>118558</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72281</t>
+          <t>70088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276075</t>
+          <t>98402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>183455</t>
+          <t>154949</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133079</t>
+          <t>136752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322250</t>
+          <t>176634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1126265</t>
+          <t>1240051</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1126265</t>
+          <t>1240051</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1126265</t>
+          <t>1240051</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>530352</t>
+          <t>584205</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258545</t>
+          <t>562614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>739905</t>
+          <t>602333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>605558</t>
+          <t>620389</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>588768</t>
+          <t>604988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>624518</t>
+          <t>634614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1135910</t>
+          <t>1204593</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>694669</t>
+          <t>1177685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1354831</t>
+          <t>1228795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>22642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>343412</t>
+          <t>100287</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128889</t>
+          <t>83232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>620062</t>
+          <t>121823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>96365</t>
+          <t>103623</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78877</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112725</t>
+          <t>118501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>439776</t>
+          <t>203910</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216532</t>
+          <t>182933</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>888093</t>
+          <t>230899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>885474</t>
+          <t>698360</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>885474</t>
+          <t>698360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>885474</t>
+          <t>698360</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711581</t>
+          <t>735552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711581</t>
+          <t>735552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711581</t>
+          <t>735552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597055</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597055</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597055</t>
+          <t>1433912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>485637</t>
+          <t>523045</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>470126</t>
+          <t>506425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>500438</t>
+          <t>539594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>459706</t>
+          <t>512017</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>446793</t>
+          <t>498005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>471723</t>
+          <t>524550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>945343</t>
+          <t>1035061</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924859</t>
+          <t>1012746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964863</t>
+          <t>1055596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -2662,102 +2662,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>3091</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>12271</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4714</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>5766</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>12022</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>69274</t>
+          <t>79888</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>63755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84831</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>83940</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96312</t>
+          <t>105584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>153214</t>
+          <t>171570</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133791</t>
+          <t>152013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172767</t>
+          <t>193060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>559293</t>
+          <t>607357</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559293</t>
+          <t>607357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559293</t>
+          <t>607357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>545031</t>
+          <t>605644</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545031</t>
+          <t>605644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545031</t>
+          <t>605644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1104323</t>
+          <t>1213001</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1104323</t>
+          <t>1213001</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1104323</t>
+          <t>1213001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,27 +3005,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>312344</t>
+          <t>344758</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>300881</t>
+          <t>330679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>322177</t>
+          <t>356291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>545892</t>
+          <t>370337</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>510327</t>
+          <t>360263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>584242</t>
+          <t>381494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>858237</t>
+          <t>715095</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>820905</t>
+          <t>697655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>916213</t>
+          <t>730608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -3118,22 +3118,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>52680</t>
+          <t>58874</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42505</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63465</t>
+          <t>73329</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>63511</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>74257</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>110373</t>
+          <t>122385</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>107903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146059</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367525</t>
+          <t>406469</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367525</t>
+          <t>406469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367525</t>
+          <t>406469</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607827</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607827</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607827</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975352</t>
+          <t>845026</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975352</t>
+          <t>845026</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975352</t>
+          <t>845026</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>237545</t>
+          <t>259124</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>227508</t>
+          <t>247639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>246180</t>
+          <t>270034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>356971</t>
+          <t>387937</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>346913</t>
+          <t>376066</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>367272</t>
+          <t>399281</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>594516</t>
+          <t>647061</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>580232</t>
+          <t>631012</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>608683</t>
+          <t>661539</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>41224</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>36627</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,67 +3722,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>71357</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74258</t>
+          <t>82919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>117860</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>104376</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>135055</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>17,5%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>105280</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>91931</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>119649</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>281453</t>
+          <t>308818</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281453</t>
+          <t>308818</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>281453</t>
+          <t>308818</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462821</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462821</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462821</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>705692</t>
+          <t>771639</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>705692</t>
+          <t>771639</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>705692</t>
+          <t>771639</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2717431</t>
+          <t>2992049</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2147876</t>
+          <t>2941745</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2941233</t>
+          <t>3041609</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3089176</t>
+          <t>3169527</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2872427</t>
+          <t>3128514</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3200684</t>
+          <t>3202815</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5806606</t>
+          <t>6161577</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5088981</t>
+          <t>6098313</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6071245</t>
+          <t>6219832</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>67060</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>61555</t>
+          <t>72820</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>101236</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>692530</t>
+          <t>482539</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>466962</t>
+          <t>436883</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1275292</t>
+          <t>532983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>575527</t>
+          <t>513934</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>461635</t>
+          <t>480572</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>791573</t>
+          <t>552839</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>996473</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1000538</t>
+          <t>936725</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2000420</t>
+          <t>1062275</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
